--- a/output/pdf_financials_xlsx/GNT.H.xlsx
+++ b/output/pdf_financials_xlsx/GNT.H.xlsx
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.068984</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1152,43 +1152,43 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000142</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.086469</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.056531</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.015277</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.002209</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000212</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.0005910000000000001</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000522</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>3.2e-05</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
@@ -2245,43 +2245,43 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.097637</v>
+        <v>-0.097779</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.097637</v>
+        <v>-0.184106</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-20.106911</v>
+        <v>-20.163442</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.162625</v>
+        <v>-1.177902</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.180847</v>
+        <v>-0.183056</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.274424</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.31489</v>
+        <v>-0.315102</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.040742</v>
+        <v>-0.041333</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.295868</v>
+        <v>-0.29639</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.301085</v>
+        <v>-0.301165</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.021194</v>
+        <v>0.021162</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.257913</v>
+        <v>-0.257921</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.066591</v>
+        <v>0.066589</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2381,43 +2381,43 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.697439</v>
+        <v>0.6972969999999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.74442</v>
+        <v>0.657951</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-20.013872</v>
+        <v>-20.070403</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.115644</v>
+        <v>-1.130921</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.161049</v>
+        <v>-0.163258</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.273923</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.314635</v>
+        <v>-0.314847</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.040553</v>
+        <v>-0.041144</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.295868</v>
+        <v>-0.29639</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.301085</v>
+        <v>-0.301165</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.021194</v>
+        <v>0.021162</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.257913</v>
+        <v>-0.257921</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.066591</v>
+        <v>0.066589</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2717,34 +2717,34 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.331916</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>6.935012</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.689511</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.02791</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.294592</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.129065</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001309</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.066938</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.006054</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001034</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.004085</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.009802999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.026703</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.001558</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.001022</v>
       </c>
     </row>
     <row r="35">
@@ -2851,34 +2851,34 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>5.331916</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>6.935012</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.689511</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.02791</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.294592</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.129065</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.001309</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.066938</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.006054</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.001034</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -2886,19 +2886,19 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.004085</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.009802999999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.026703</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.001558</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.001022</v>
       </c>
     </row>
     <row r="37">
@@ -3655,34 +3655,34 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.378725</v>
+        <v>0.046809</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.01091</v>
+        <v>0.07589799999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.895069</v>
+        <v>0.205558</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.089948</v>
+        <v>0.062038</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.340953</v>
+        <v>0.046361</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.19205</v>
+        <v>0.062985</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.043043</v>
+        <v>0.041734</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.212263</v>
+        <v>0.145325</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.177413</v>
+        <v>0.171359</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.133352</v>
+        <v>0.132318</v>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.020101</v>
+        <v>0.016016</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.025085</v>
+        <v>0.015282</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.045694</v>
+        <v>0.018991</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.004409</v>
+        <v>0.002851</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.001022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -59906,7 +59906,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -68270,7 +68270,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -71006,7 +71006,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -73740,7 +73740,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -76148,7 +76148,7 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E645" s="5" t="n">
@@ -78530,7 +78530,7 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E668" s="5" t="n">

--- a/output/pdf_financials_xlsx/GNT.H.xlsx
+++ b/output/pdf_financials_xlsx/GNT.H.xlsx
@@ -1761,7 +1761,7 @@
         <v>-20.106911</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-1.162625</v>
+        <v>-1.054669</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>0.20411</v>
@@ -1773,7 +1773,7 @@
         <v>-0.301859</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.040742</v>
+        <v>-0.040569</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.295868</v>
@@ -1828,19 +1828,19 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-0.107956</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-0.384957</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-8.8e-05</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-0.013031</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-0.000173</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -7118,13 +7118,13 @@
         <v>-0.180847</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-0.274424</v>
+        <v>-0.274337</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-0.31489</v>
+        <v>-0.301859</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>-0.31489</v>
+        <v>-0.040569</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-0.295868</v>
@@ -22982,7 +22982,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -25760,7 +25764,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -30036,11 +30044,7 @@
           <t>Net (loss) income from continuing operations $</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -32418,7 +32422,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -62510,7 +62518,11 @@
           <t>Net loss from discontinued operations (note 7)</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -63660,7 +63672,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E526" t="inlineStr">
         <is>
           <t>-</t>
@@ -63762,7 +63778,11 @@
           <t>Net loss from discontinued operations (note 6)</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E527" t="inlineStr">
         <is>
           <t>-</t>
@@ -64696,7 +64716,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr">
         <is>
           <t>-</t>
@@ -66372,7 +66396,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -66474,7 +66502,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -68586,7 +68618,11 @@
           <t>Net loss from discontinued operations (note 8) -</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E573" t="inlineStr">
         <is>
           <t>-</t>
